--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R7" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,16 +1384,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1403,20 +1402,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R9" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R10" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,11 +1546,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B11" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R11" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,6 +1643,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>80053</v>
+        <v>91851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R12" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>91851</v>
+        <v>80053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R13" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129661752</v>
+        <v>129661753</v>
       </c>
       <c r="B15" t="n">
         <v>92006</v>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741091</v>
+        <v>741071</v>
       </c>
       <c r="R15" t="n">
-        <v>7125499</v>
+        <v>7125530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129661753</v>
+        <v>129661752</v>
       </c>
       <c r="B16" t="n">
         <v>92006</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741071</v>
+        <v>741091</v>
       </c>
       <c r="R16" t="n">
-        <v>7125530</v>
+        <v>7125499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661758</v>
+        <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741165</v>
+        <v>741196</v>
       </c>
       <c r="R20" t="n">
-        <v>7125448</v>
+        <v>7125593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,11 +2531,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2562,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R21" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661773</v>
+        <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741161</v>
+        <v>741165</v>
       </c>
       <c r="R22" t="n">
-        <v>7125467</v>
+        <v>7125448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,6 +2725,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R24" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R25" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129661747</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129661762</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129661759</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R5" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R6" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741118</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,34 +1283,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R8" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,7 +1376,7 @@
         <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B10" t="n">
-        <v>91851</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R10" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,6 +1546,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>91879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R11" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,11 +1648,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,7 +1677,7 @@
         <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129661764</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R18" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2332,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,21 +2369,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2398,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R19" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2429,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2463,7 +2463,7 @@
         <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661773</v>
+        <v>129661758</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741161</v>
+        <v>741165</v>
       </c>
       <c r="R21" t="n">
-        <v>7125467</v>
+        <v>7125448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,6 +2628,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661758</v>
+        <v>129661773</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741165</v>
+        <v>741161</v>
       </c>
       <c r="R22" t="n">
-        <v>7125448</v>
+        <v>7125467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,11 +2730,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2759,7 +2759,7 @@
         <v>129661757</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R24" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R25" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R18" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2398,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R19" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,11 +2434,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R20" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661758</v>
+        <v>129661767</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741165</v>
+        <v>741196</v>
       </c>
       <c r="R21" t="n">
-        <v>7125448</v>
+        <v>7125593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,11 +2628,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661773</v>
+        <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741161</v>
+        <v>741165</v>
       </c>
       <c r="R22" t="n">
-        <v>7125467</v>
+        <v>7125448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,6 +2725,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129661747</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129661762</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129661759</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R5" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R6" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1178,7 @@
         <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>129661750</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>129661756</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>129661755</v>
       </c>
       <c r="B11" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B12" t="n">
-        <v>91879</v>
+        <v>80084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R12" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B13" t="n">
-        <v>80079</v>
+        <v>91885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R13" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129661764</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R18" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2332,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,21 +2369,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2398,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R19" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2429,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R20" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661767</v>
+        <v>129661758</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741196</v>
+        <v>741165</v>
       </c>
       <c r="R21" t="n">
-        <v>7125593</v>
+        <v>7125448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,6 +2628,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661758</v>
+        <v>129661773</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741165</v>
+        <v>741161</v>
       </c>
       <c r="R22" t="n">
-        <v>7125448</v>
+        <v>7125467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,11 +2730,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2759,7 +2759,7 @@
         <v>129661757</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B24" t="n">
-        <v>91581</v>
+        <v>79075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R24" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R25" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129661747</v>
       </c>
       <c r="B2" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129661762</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129661759</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129661761</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B7" t="n">
-        <v>80180</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R7" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,16 +1287,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,20 +1305,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R8" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R9" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>91886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R10" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,11 +1546,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B11" t="n">
-        <v>91885</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R11" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,6 +1643,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,7 +1677,7 @@
         <v>129661751</v>
       </c>
       <c r="B12" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129661754</v>
       </c>
       <c r="B13" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129661764</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R18" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2398,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R19" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,11 +2434,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2463,7 +2463,7 @@
         <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661758</v>
+        <v>129661773</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741165</v>
+        <v>741161</v>
       </c>
       <c r="R21" t="n">
-        <v>7125448</v>
+        <v>7125467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,11 +2628,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661773</v>
+        <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741161</v>
+        <v>741165</v>
       </c>
       <c r="R22" t="n">
-        <v>7125467</v>
+        <v>7125448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,6 +2725,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2759,7 +2759,7 @@
         <v>129661757</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R24" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R25" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741118</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661750</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,16 +1283,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1305,16 +1301,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>740939</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661768</v>
+        <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741118</v>
+        <v>741074</v>
       </c>
       <c r="R9" t="n">
-        <v>7125616</v>
+        <v>7125538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>80085</v>
+        <v>91886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R12" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>91886</v>
+        <v>80085</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R13" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R18" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2332,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,21 +2369,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2398,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R19" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2429,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B10" t="n">
-        <v>91886</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R10" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,6 +1546,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R11" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,11 +1648,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,7 +1677,7 @@
         <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R20" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R21" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B24" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R24" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B25" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R25" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R10" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,11 +1546,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B11" t="n">
-        <v>91891</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R11" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,6 +1643,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>80090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R12" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B13" t="n">
-        <v>80090</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R13" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R7" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,16 +1287,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,20 +1305,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R8" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R9" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R20" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R21" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R5" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R6" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661768</v>
+        <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741118</v>
+        <v>741074</v>
       </c>
       <c r="R9" t="n">
-        <v>7125616</v>
+        <v>7125538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R12" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>80090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R13" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R24" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R25" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661768</v>
+        <v>129661760</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741118</v>
+        <v>741074</v>
       </c>
       <c r="R8" t="n">
-        <v>7125616</v>
+        <v>7125538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R9" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,7 +1478,7 @@
         <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661767</v>
+        <v>129661758</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741196</v>
+        <v>741165</v>
       </c>
       <c r="R20" t="n">
-        <v>7125593</v>
+        <v>7125448</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,6 +2531,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2557,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2573,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R21" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661758</v>
+        <v>129661773</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741165</v>
+        <v>741161</v>
       </c>
       <c r="R22" t="n">
-        <v>7125448</v>
+        <v>7125467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,11 +2730,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2861,7 +2861,7 @@
         <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R5" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R6" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741118</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,34 +1385,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R9" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661758</v>
+        <v>129661773</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741165</v>
+        <v>741161</v>
       </c>
       <c r="R20" t="n">
-        <v>7125448</v>
+        <v>7125467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,11 +2531,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661773</v>
+        <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2665,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2689,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741161</v>
+        <v>741165</v>
       </c>
       <c r="R22" t="n">
-        <v>7125467</v>
+        <v>7125448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2730,6 +2725,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B24" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R24" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R25" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B12" t="n">
-        <v>91897</v>
+        <v>80090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R12" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B13" t="n">
-        <v>80090</v>
+        <v>91897</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R13" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B10" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R10" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,6 +1546,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,10 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1612,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R11" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,11 +1648,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R20" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R21" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R5" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R6" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129661747</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129661762</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129661759</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R5" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R6" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1178,7 @@
         <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661750</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,16 +1301,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>740939</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,16 +1384,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1403,20 +1402,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R9" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129661756</v>
+        <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741166</v>
+        <v>741069</v>
       </c>
       <c r="R10" t="n">
-        <v>7125623</v>
+        <v>7125541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,11 +1546,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1577,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129661755</v>
+        <v>129661756</v>
       </c>
       <c r="B11" t="n">
-        <v>91897</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1612,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741069</v>
+        <v>741166</v>
       </c>
       <c r="R11" t="n">
-        <v>7125541</v>
+        <v>7125623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,6 +1643,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>80090</v>
+        <v>91900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R12" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>91897</v>
+        <v>80093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R13" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129661764</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R18" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2398,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R19" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,11 +2434,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2463,7 +2463,7 @@
         <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>129661773</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>129661757</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2858,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129661772</v>
+        <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>741126</v>
+        <v>741066</v>
       </c>
       <c r="R24" t="n">
-        <v>7125873</v>
+        <v>7125531</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,10 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129661746</v>
+        <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2966,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>741066</v>
+        <v>741126</v>
       </c>
       <c r="R25" t="n">
-        <v>7125531</v>
+        <v>7125873</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R7" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,16 +1287,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,20 +1305,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R8" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R9" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R18" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,11 +2332,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2363,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,21 +2369,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2398,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R19" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2429,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129661747</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129661762</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129661759</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R5" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R6" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661768</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,38 +1186,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741118</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661750</v>
       </c>
       <c r="B8" t="n">
         <v>57737</v>
@@ -1287,16 +1283,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1305,16 +1301,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>740939</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125650</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661768</v>
+        <v>129661760</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741118</v>
+        <v>741074</v>
       </c>
       <c r="R9" t="n">
-        <v>7125616</v>
+        <v>7125538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,7 +1478,7 @@
         <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>129661756</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>129661764</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>129661774</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>129661763</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B20" t="n">
-        <v>80189</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R20" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R21" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,7 +2657,7 @@
         <v>129661758</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>129661757</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R5" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R6" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2557,10 +2557,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129661767</v>
+        <v>129661758</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741196</v>
+        <v>741165</v>
       </c>
       <c r="R21" t="n">
-        <v>7125593</v>
+        <v>7125448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,6 +2628,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661758</v>
+        <v>129661767</v>
       </c>
       <c r="B22" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2665,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2689,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741165</v>
+        <v>741196</v>
       </c>
       <c r="R22" t="n">
-        <v>7125448</v>
+        <v>7125593</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,11 +2730,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129661775</v>
+        <v>129661761</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740939</v>
+        <v>741173</v>
       </c>
       <c r="R5" t="n">
-        <v>7125650</v>
+        <v>7125642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129661761</v>
+        <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741173</v>
+        <v>740939</v>
       </c>
       <c r="R6" t="n">
-        <v>7125642</v>
+        <v>7125650</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1081,7 +1081,7 @@
         <v>129661775</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,34 +1186,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R7" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,16 +1287,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1301,20 +1305,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R8" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R9" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,7 +1478,7 @@
         <v>129661755</v>
       </c>
       <c r="B10" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B12" t="n">
-        <v>91903</v>
+        <v>80097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R12" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B13" t="n">
-        <v>80096</v>
+        <v>91904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R13" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,7 +1871,7 @@
         <v>129661745</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>129661753</v>
       </c>
       <c r="B15" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>129661752</v>
       </c>
       <c r="B16" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129661774</v>
+        <v>129661763</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741182</v>
+        <v>741166</v>
       </c>
       <c r="R18" t="n">
-        <v>7125493</v>
+        <v>7125449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,6 +2332,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129661763</v>
+        <v>129661774</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2369,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2398,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741166</v>
+        <v>741182</v>
       </c>
       <c r="R19" t="n">
-        <v>7125449</v>
+        <v>7125493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,11 +2434,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2460,10 +2460,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129661773</v>
+        <v>129661767</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,21 +2471,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741161</v>
+        <v>741196</v>
       </c>
       <c r="R20" t="n">
-        <v>7125467</v>
+        <v>7125593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129661767</v>
+        <v>129661773</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>741196</v>
+        <v>741161</v>
       </c>
       <c r="R22" t="n">
-        <v>7125593</v>
+        <v>7125467</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,7 +2861,7 @@
         <v>129661746</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>129661772</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 60849-2024 artfynd.xlsx
+++ b/artfynd/A 60849-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129661750</v>
+        <v>129661760</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1204,20 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740939</v>
+        <v>741074</v>
       </c>
       <c r="R7" t="n">
-        <v>7125650</v>
+        <v>7125538</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129661760</v>
+        <v>129661768</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741074</v>
+        <v>741118</v>
       </c>
       <c r="R8" t="n">
-        <v>7125538</v>
+        <v>7125616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129661768</v>
+        <v>129661750</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,34 +1385,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högkläppen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741118</v>
+        <v>740939</v>
       </c>
       <c r="R9" t="n">
-        <v>7125616</v>
+        <v>7125650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,32 +1674,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129661751</v>
+        <v>129661754</v>
       </c>
       <c r="B12" t="n">
-        <v>80097</v>
+        <v>91904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741116</v>
+        <v>741066</v>
       </c>
       <c r="R12" t="n">
-        <v>7125615</v>
+        <v>7125531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,32 +1771,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129661754</v>
+        <v>129661751</v>
       </c>
       <c r="B13" t="n">
-        <v>91904</v>
+        <v>80097</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741066</v>
+        <v>741116</v>
       </c>
       <c r="R13" t="n">
-        <v>7125531</v>
+        <v>7125615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
